--- a/knowledge_base/source/07_evaluation_rules.xlsx
+++ b/knowledge_base/source/07_evaluation_rules.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_evaluation_rules" sheetId="1" r:id="R7c2af201409a4339"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_evaluation_rules" sheetId="1" r:id="R1966b77c44fb4c30"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1393,10 +1393,10 @@
         <x:v>The assessment section cannot be extracted reliably.</x:v>
       </x:c>
       <x:c r="I27" s="32" t="str">
-        <x:v>Assessment comparison is not requested.</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="J27" s="32" t="str">
-        <x:v>Satisfied; Partially Satisfied; Not Satisfied; Not Verified; Not Applicable</x:v>
+        <x:v>Satisfied; Partially Satisfied; Not Satisfied; Not Verified</x:v>
       </x:c>
       <x:c r="K27" s="38" t="str">
         <x:v>System Rule</x:v>
@@ -1545,7 +1545,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73f251d85bab4be6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb07deec464204c13"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/knowledge_base/source/07_evaluation_rules.xlsx
+++ b/knowledge_base/source/07_evaluation_rules.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_evaluation_rules" sheetId="1" r:id="R1966b77c44fb4c30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_evaluation_rules" sheetId="1" r:id="R10418c63329c430f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -166,7 +166,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="42">
+  <x:cellXfs count="43">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -269,6 +269,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -856,13 +857,13 @@
         <x:v>Language Rule</x:v>
       </x:c>
       <x:c r="E12" s="32" t="str">
-        <x:v>The question contains a clear action and expected response.</x:v>
+        <x:v>The question states a clear action and recognizable expected response or output.</x:v>
       </x:c>
       <x:c r="F12" s="32" t="str">
-        <x:v>The expected task is understandable but not fully precise.</x:v>
+        <x:v>The action is recognizable but the expected response or output is not fully precise.</x:v>
       </x:c>
       <x:c r="G12" s="32" t="str">
-        <x:v>The task or expected response cannot be identified.</x:v>
+        <x:v>The required action or expected response cannot be identified.</x:v>
       </x:c>
       <x:c r="H12" s="32" t="str">
         <x:v>Question text is unreadable or OCR confidence is insufficient.</x:v>
@@ -891,13 +892,13 @@
         <x:v>Language Rule</x:v>
       </x:c>
       <x:c r="E13" s="32" t="str">
-        <x:v>The question wording is sufficiently precise for consistent interpretation.</x:v>
+        <x:v>The wording contains no material linguistic ambiguity, contradiction, or unclear terminology.</x:v>
       </x:c>
       <x:c r="F13" s="32" t="str">
-        <x:v>The question contains minor ambiguity but remains answerable.</x:v>
+        <x:v>A minor linguistic ambiguity exists but the intended interpretation remains reasonably consistent.</x:v>
       </x:c>
       <x:c r="G13" s="32" t="str">
-        <x:v>The question contains material ambiguity contradiction or missing conditions affecting answerability.</x:v>
+        <x:v>The wording contains material linguistic ambiguity, contradiction, or unclear terminology that permits different interpretations.</x:v>
       </x:c>
       <x:c r="H13" s="32" t="str">
         <x:v>Question text is missing or unreadable.</x:v>
@@ -926,16 +927,16 @@
         <x:v>Content Rule</x:v>
       </x:c>
       <x:c r="E14" s="32" t="str">
-        <x:v>The question contains all information necessary for the expected answer.</x:v>
+        <x:v>The question and its confirmed question-specific context contain all information necessary for the expected answer.</x:v>
       </x:c>
       <x:c r="F14" s="32" t="str">
-        <x:v>A minor detail is missing but the question remains answerable.</x:v>
+        <x:v>A minor question-specific detail is missing but the question remains answerable.</x:v>
       </x:c>
       <x:c r="G14" s="32" t="str">
-        <x:v>Essential information conditions data or context are missing.</x:v>
+        <x:v>Essential data, conditions, or confirmed referenced context are missing.</x:v>
       </x:c>
       <x:c r="H14" s="32" t="str">
-        <x:v>Question or surrounding context is unreadable.</x:v>
+        <x:v>Question text or required confirmed context is unreadable or cannot be associated reliably.</x:v>
       </x:c>
       <x:c r="I14" s="32" t="str">
         <x:v>None</x:v>
@@ -1206,19 +1207,19 @@
         <x:v>Instruction Rule</x:v>
       </x:c>
       <x:c r="E22" s="32" t="str">
-        <x:v>All necessary general and question-specific instructions are present.</x:v>
+        <x:v>All necessary exam-level general instructions are present.</x:v>
       </x:c>
       <x:c r="F22" s="32" t="str">
-        <x:v>Instructions are generally sufficient but one detail is incomplete.</x:v>
+        <x:v>The exam-level general instructions are generally sufficient but one relevant detail is incomplete.</x:v>
       </x:c>
       <x:c r="G22" s="32" t="str">
-        <x:v>A necessary instruction is missing and affects interpretation or completion.</x:v>
+        <x:v>A necessary exam-level general instruction is missing and affects completion of the exam.</x:v>
       </x:c>
       <x:c r="H22" s="32" t="str">
-        <x:v>Instruction text is unreadable.</x:v>
+        <x:v>Exam-level general instruction text is unreadable.</x:v>
       </x:c>
       <x:c r="I22" s="32" t="str">
-        <x:v>No special instruction is required.</x:v>
+        <x:v>No additional exam-level general instruction is needed.</x:v>
       </x:c>
       <x:c r="J22" s="32" t="str">
         <x:v>Satisfied; Partially Satisfied; Not Satisfied; Not Verified; Not Applicable</x:v>
@@ -1545,7 +1546,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb07deec464204c13"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra31b57e4adc14c2b"/>
   </x:tableParts>
 </x:worksheet>
 </file>